--- a/artfynd/A 2214-2024 artfynd.xlsx
+++ b/artfynd/A 2214-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123890958</v>
       </c>
       <c r="B2" t="n">
-        <v>57509</v>
+        <v>57510</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123890805</v>
+        <v>123890264</v>
       </c>
       <c r="B3" t="n">
-        <v>57641</v>
+        <v>57497</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,16 +805,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103020</v>
+        <v>100048</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -877,6 +877,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>ivrigt trummande</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123890264</v>
+        <v>123890805</v>
       </c>
       <c r="B4" t="n">
-        <v>57496</v>
+        <v>57642</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,16 +924,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100048</v>
+        <v>103020</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -938,7 +943,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -991,11 +996,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-14</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>ivrigt trummande</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 2214-2024 artfynd.xlsx
+++ b/artfynd/A 2214-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123890958</v>
+        <v>123890264</v>
       </c>
       <c r="B2" t="n">
-        <v>57510</v>
+        <v>57497</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102977</v>
+        <v>100048</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -763,6 +763,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>ivrigt trummande</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123890264</v>
+        <v>123890805</v>
       </c>
       <c r="B3" t="n">
-        <v>57497</v>
+        <v>57642</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,16 +810,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100048</v>
+        <v>103020</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -824,7 +829,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -877,11 +882,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-14</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>ivrigt trummande</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123890805</v>
+        <v>123890958</v>
       </c>
       <c r="B4" t="n">
-        <v>57642</v>
+        <v>57510</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,25 +920,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103020</v>
+        <v>102977</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">

--- a/artfynd/A 2214-2024 artfynd.xlsx
+++ b/artfynd/A 2214-2024 artfynd.xlsx
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123890805</v>
+        <v>123890958</v>
       </c>
       <c r="B3" t="n">
-        <v>57642</v>
+        <v>57510</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,25 +806,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103020</v>
+        <v>102977</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -908,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123890958</v>
+        <v>123890805</v>
       </c>
       <c r="B4" t="n">
-        <v>57510</v>
+        <v>57642</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,25 +920,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102977</v>
+        <v>103020</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">

--- a/artfynd/A 2214-2024 artfynd.xlsx
+++ b/artfynd/A 2214-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123890264</v>
+        <v>123890805</v>
       </c>
       <c r="B2" t="n">
-        <v>57497</v>
+        <v>57642</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100048</v>
+        <v>103020</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -763,11 +763,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-14</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>ivrigt trummande</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -908,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123890805</v>
+        <v>123890264</v>
       </c>
       <c r="B4" t="n">
-        <v>57642</v>
+        <v>57497</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,16 +919,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103020</v>
+        <v>100048</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -943,7 +938,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -996,6 +991,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>ivrigt trummande</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 2214-2024 artfynd.xlsx
+++ b/artfynd/A 2214-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123890805</v>
+        <v>123890958</v>
       </c>
       <c r="B2" t="n">
-        <v>57642</v>
+        <v>57510</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103020</v>
+        <v>102977</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123890958</v>
+        <v>123890264</v>
       </c>
       <c r="B3" t="n">
-        <v>57510</v>
+        <v>57497</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,30 +801,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102977</v>
+        <v>100048</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -877,6 +877,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>ivrigt trummande</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123890264</v>
+        <v>123890805</v>
       </c>
       <c r="B4" t="n">
-        <v>57497</v>
+        <v>57642</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,16 +924,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100048</v>
+        <v>103020</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -938,7 +943,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -991,11 +996,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-14</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>ivrigt trummande</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 2214-2024 artfynd.xlsx
+++ b/artfynd/A 2214-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123890805</v>
+        <v>123890264</v>
       </c>
       <c r="B2" t="n">
-        <v>57664</v>
+        <v>57519</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103020</v>
+        <v>100048</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -763,6 +763,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>ivrigt trummande</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123890264</v>
+        <v>123890805</v>
       </c>
       <c r="B3" t="n">
-        <v>57519</v>
+        <v>57664</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,16 +810,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100048</v>
+        <v>103020</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -824,7 +829,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -877,11 +882,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-14</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>ivrigt trummande</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 2214-2024 artfynd.xlsx
+++ b/artfynd/A 2214-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123890264</v>
+        <v>123890805</v>
       </c>
       <c r="B2" t="n">
-        <v>57519</v>
+        <v>57664</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100048</v>
+        <v>103020</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -763,11 +763,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-14</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>ivrigt trummande</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123890805</v>
+        <v>123890958</v>
       </c>
       <c r="B3" t="n">
-        <v>57664</v>
+        <v>57532</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,25 +801,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103020</v>
+        <v>102977</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -908,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123890958</v>
+        <v>123890264</v>
       </c>
       <c r="B4" t="n">
-        <v>57532</v>
+        <v>57519</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,30 +915,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102977</v>
+        <v>100048</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -996,6 +991,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>ivrigt trummande</t>
         </is>
       </c>
       <c r="AD4" t="b">
